--- a/Region_results/Region_Forecasting_26_0805_0811.xlsx
+++ b/Region_results/Region_Forecasting_26_0805_0811.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lena/forecasting_new/Region_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F800EF26-2C60-E242-91E2-E9DADA34AD21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB0E71A-D501-5246-8BAA-4DF50E90DD83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34100" yWindow="2340" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -267,7 +267,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -332,7 +332,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -637,6 +637,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D533"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="1" width="13.1640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
@@ -674,7 +677,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>280.35000000000002</v>
+        <v>302.82</v>
       </c>
       <c r="D3">
         <v>224.83563232421881</v>
@@ -688,7 +691,7 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>277.42</v>
+        <v>311.02999999999997</v>
       </c>
       <c r="D4">
         <v>228.50547790527341</v>
@@ -772,7 +775,7 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>253.39</v>
+        <v>273.7</v>
       </c>
       <c r="D10">
         <v>199.34028625488281</v>
@@ -786,7 +789,7 @@
         <v>5</v>
       </c>
       <c r="C11">
-        <v>245.56</v>
+        <v>275.31</v>
       </c>
       <c r="D11">
         <v>194.2652282714844</v>
@@ -870,7 +873,7 @@
         <v>6</v>
       </c>
       <c r="C17">
-        <v>217.26</v>
+        <v>234.68</v>
       </c>
       <c r="D17">
         <v>172.927490234375</v>
@@ -884,7 +887,7 @@
         <v>6</v>
       </c>
       <c r="C18">
-        <v>211.12</v>
+        <v>236.7</v>
       </c>
       <c r="D18">
         <v>170.77400207519531</v>
@@ -968,7 +971,7 @@
         <v>7</v>
       </c>
       <c r="C24">
-        <v>60</v>
+        <v>64.81</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -982,7 +985,7 @@
         <v>7</v>
       </c>
       <c r="C25">
-        <v>59</v>
+        <v>66.150000000000006</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1066,7 +1069,7 @@
         <v>8</v>
       </c>
       <c r="C31">
-        <v>258.25</v>
+        <v>278.95</v>
       </c>
       <c r="D31">
         <v>211.41481018066409</v>
@@ -1080,7 +1083,7 @@
         <v>8</v>
       </c>
       <c r="C32">
-        <v>244.64</v>
+        <v>274.27999999999997</v>
       </c>
       <c r="D32">
         <v>195.29557800292969</v>
@@ -1164,7 +1167,7 @@
         <v>9</v>
       </c>
       <c r="C38">
-        <v>170.94</v>
+        <v>184.64</v>
       </c>
       <c r="D38">
         <v>140.8620910644531</v>
@@ -1178,7 +1181,7 @@
         <v>9</v>
       </c>
       <c r="C39">
-        <v>159.44999999999999</v>
+        <v>178.77</v>
       </c>
       <c r="D39">
         <v>133.52442932128909</v>
@@ -1262,7 +1265,7 @@
         <v>10</v>
       </c>
       <c r="C45">
-        <v>207.19</v>
+        <v>223.8</v>
       </c>
       <c r="D45">
         <v>161.1745300292969</v>
@@ -1276,7 +1279,7 @@
         <v>10</v>
       </c>
       <c r="C46">
-        <v>202.38</v>
+        <v>226.9</v>
       </c>
       <c r="D46">
         <v>166.29290771484381</v>
@@ -1360,7 +1363,7 @@
         <v>11</v>
       </c>
       <c r="C52">
-        <v>309.2</v>
+        <v>333.98</v>
       </c>
       <c r="D52">
         <v>244.1295166015625</v>
@@ -1374,7 +1377,7 @@
         <v>11</v>
       </c>
       <c r="C53">
-        <v>312.52</v>
+        <v>350.38</v>
       </c>
       <c r="D53">
         <v>238.91191101074219</v>
@@ -1458,7 +1461,7 @@
         <v>12</v>
       </c>
       <c r="C59">
-        <v>248.32</v>
+        <v>268.22000000000003</v>
       </c>
       <c r="D59">
         <v>190.3916931152344</v>
@@ -1472,7 +1475,7 @@
         <v>12</v>
       </c>
       <c r="C60">
-        <v>248.07</v>
+        <v>278.13</v>
       </c>
       <c r="D60">
         <v>181.82466125488281</v>
@@ -1556,7 +1559,7 @@
         <v>13</v>
       </c>
       <c r="C66">
-        <v>654.71</v>
+        <v>707.19</v>
       </c>
       <c r="D66">
         <v>539.80426025390625</v>
@@ -1570,7 +1573,7 @@
         <v>13</v>
       </c>
       <c r="C67">
-        <v>622.36</v>
+        <v>697.76</v>
       </c>
       <c r="D67">
         <v>504.085693359375</v>
@@ -1654,7 +1657,7 @@
         <v>14</v>
       </c>
       <c r="C73">
-        <v>424.23</v>
+        <v>458.24</v>
       </c>
       <c r="D73">
         <v>322.84912109375</v>
@@ -1668,7 +1671,7 @@
         <v>14</v>
       </c>
       <c r="C74">
-        <v>403.32</v>
+        <v>452.19</v>
       </c>
       <c r="D74">
         <v>320.32080078125</v>
@@ -1752,7 +1755,7 @@
         <v>15</v>
       </c>
       <c r="C80">
-        <v>208.06</v>
+        <v>224.74</v>
       </c>
       <c r="D80">
         <v>168.70964050292969</v>
@@ -1766,7 +1769,7 @@
         <v>15</v>
       </c>
       <c r="C81">
-        <v>200.86</v>
+        <v>225.2</v>
       </c>
       <c r="D81">
         <v>162.26234436035159</v>
@@ -1850,7 +1853,7 @@
         <v>16</v>
       </c>
       <c r="C87">
-        <v>173.83</v>
+        <v>187.76</v>
       </c>
       <c r="D87">
         <v>151.43019104003909</v>
@@ -1864,7 +1867,7 @@
         <v>16</v>
       </c>
       <c r="C88">
-        <v>172.51</v>
+        <v>193.41</v>
       </c>
       <c r="D88">
         <v>149.04815673828119</v>
@@ -1948,7 +1951,7 @@
         <v>17</v>
       </c>
       <c r="C94">
-        <v>324.02</v>
+        <v>349.99</v>
       </c>
       <c r="D94">
         <v>247.64057922363281</v>
@@ -1962,7 +1965,7 @@
         <v>17</v>
       </c>
       <c r="C95">
-        <v>315.98</v>
+        <v>354.26</v>
       </c>
       <c r="D95">
         <v>250.32279968261719</v>
@@ -2046,7 +2049,7 @@
         <v>18</v>
       </c>
       <c r="C101">
-        <v>415.7</v>
+        <v>449.02</v>
       </c>
       <c r="D101">
         <v>331.53451538085938</v>
@@ -2060,7 +2063,7 @@
         <v>18</v>
       </c>
       <c r="C102">
-        <v>398.01</v>
+        <v>446.23</v>
       </c>
       <c r="D102">
         <v>322.05880737304688</v>
@@ -2144,7 +2147,7 @@
         <v>19</v>
       </c>
       <c r="C108">
-        <v>220.06</v>
+        <v>237.7</v>
       </c>
       <c r="D108">
         <v>172.32145690917969</v>
@@ -2158,7 +2161,7 @@
         <v>19</v>
       </c>
       <c r="C109">
-        <v>196.63</v>
+        <v>220.45</v>
       </c>
       <c r="D109">
         <v>163.42878723144531</v>
@@ -2242,7 +2245,7 @@
         <v>20</v>
       </c>
       <c r="C115">
-        <v>215.97</v>
+        <v>233.28</v>
       </c>
       <c r="D115">
         <v>173.5184020996094</v>
@@ -2256,7 +2259,7 @@
         <v>20</v>
       </c>
       <c r="C116">
-        <v>192.06</v>
+        <v>215.33</v>
       </c>
       <c r="D116">
         <v>155.64442443847659</v>
@@ -2340,7 +2343,7 @@
         <v>21</v>
       </c>
       <c r="C122">
-        <v>234.91</v>
+        <v>253.74</v>
       </c>
       <c r="D122">
         <v>182.07720947265619</v>
@@ -2354,7 +2357,7 @@
         <v>21</v>
       </c>
       <c r="C123">
-        <v>216.05</v>
+        <v>242.23</v>
       </c>
       <c r="D123">
         <v>175.61810302734381</v>
@@ -2438,7 +2441,7 @@
         <v>22</v>
       </c>
       <c r="C129">
-        <v>79.55</v>
+        <v>85.93</v>
       </c>
       <c r="D129">
         <v>64.150474548339844</v>
@@ -2452,7 +2455,7 @@
         <v>22</v>
       </c>
       <c r="C130">
-        <v>79.349999999999994</v>
+        <v>88.96</v>
       </c>
       <c r="D130">
         <v>61.997650146484382</v>
@@ -2536,7 +2539,7 @@
         <v>23</v>
       </c>
       <c r="C136">
-        <v>223.69</v>
+        <v>241.62</v>
       </c>
       <c r="D136">
         <v>191.29090881347659</v>
@@ -2550,7 +2553,7 @@
         <v>23</v>
       </c>
       <c r="C137">
-        <v>219.99</v>
+        <v>246.64</v>
       </c>
       <c r="D137">
         <v>183.54011535644531</v>
@@ -2634,7 +2637,7 @@
         <v>24</v>
       </c>
       <c r="C143">
-        <v>201.5</v>
+        <v>217.65</v>
       </c>
       <c r="D143">
         <v>171.36236572265619</v>
@@ -2648,7 +2651,7 @@
         <v>24</v>
       </c>
       <c r="C144">
-        <v>196.73</v>
+        <v>220.57</v>
       </c>
       <c r="D144">
         <v>171.21087646484381</v>
@@ -2732,7 +2735,7 @@
         <v>25</v>
       </c>
       <c r="C150">
-        <v>305.87</v>
+        <v>330.39</v>
       </c>
       <c r="D150">
         <v>242.18096923828119</v>
@@ -2746,7 +2749,7 @@
         <v>25</v>
       </c>
       <c r="C151">
-        <v>294.86</v>
+        <v>330.58</v>
       </c>
       <c r="D151">
         <v>227.47755432128909</v>
@@ -2830,7 +2833,7 @@
         <v>26</v>
       </c>
       <c r="C157">
-        <v>176.25</v>
+        <v>190.38</v>
       </c>
       <c r="D157">
         <v>148.4579772949219</v>
@@ -2844,7 +2847,7 @@
         <v>26</v>
       </c>
       <c r="C158">
-        <v>170.84</v>
+        <v>191.54</v>
       </c>
       <c r="D158">
         <v>142.2939453125</v>
@@ -2928,7 +2931,7 @@
         <v>27</v>
       </c>
       <c r="C164">
-        <v>8</v>
+        <v>8.64</v>
       </c>
       <c r="D164">
         <v>0</v>
@@ -2942,7 +2945,7 @@
         <v>27</v>
       </c>
       <c r="C165">
-        <v>8</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="D165">
         <v>0</v>
@@ -3026,7 +3029,7 @@
         <v>28</v>
       </c>
       <c r="C171">
-        <v>342.81</v>
+        <v>370.29</v>
       </c>
       <c r="D171">
         <v>273.85885620117188</v>
@@ -3040,7 +3043,7 @@
         <v>28</v>
       </c>
       <c r="C172">
-        <v>307.8</v>
+        <v>345.09</v>
       </c>
       <c r="D172">
         <v>259.64776611328119</v>
@@ -3124,7 +3127,7 @@
         <v>29</v>
       </c>
       <c r="C178">
-        <v>311.02999999999997</v>
+        <v>335.96</v>
       </c>
       <c r="D178">
         <v>228.06935119628909</v>
@@ -3138,7 +3141,7 @@
         <v>29</v>
       </c>
       <c r="C179">
-        <v>297.88</v>
+        <v>333.97</v>
       </c>
       <c r="D179">
         <v>215.55113220214841</v>
@@ -3222,7 +3225,7 @@
         <v>30</v>
       </c>
       <c r="C185">
-        <v>15</v>
+        <v>16.2</v>
       </c>
       <c r="D185">
         <v>0</v>
@@ -3236,7 +3239,7 @@
         <v>30</v>
       </c>
       <c r="C186">
-        <v>15</v>
+        <v>16.82</v>
       </c>
       <c r="D186">
         <v>0</v>
@@ -3320,7 +3323,7 @@
         <v>31</v>
       </c>
       <c r="C192">
-        <v>379.6</v>
+        <v>410.03</v>
       </c>
       <c r="D192">
         <v>322.2955322265625</v>
@@ -3334,7 +3337,7 @@
         <v>31</v>
       </c>
       <c r="C193">
-        <v>370.23</v>
+        <v>415.09</v>
       </c>
       <c r="D193">
         <v>305.75823974609381</v>
@@ -3418,7 +3421,7 @@
         <v>32</v>
       </c>
       <c r="C199">
-        <v>247.21</v>
+        <v>267.02999999999997</v>
       </c>
       <c r="D199">
         <v>191.40069580078119</v>
@@ -3432,7 +3435,7 @@
         <v>32</v>
       </c>
       <c r="C200">
-        <v>245.16</v>
+        <v>274.86</v>
       </c>
       <c r="D200">
         <v>195.63311767578119</v>
@@ -3516,7 +3519,7 @@
         <v>33</v>
       </c>
       <c r="C206">
-        <v>229.9</v>
+        <v>248.33</v>
       </c>
       <c r="D206">
         <v>185.25799560546881</v>
@@ -3530,7 +3533,7 @@
         <v>33</v>
       </c>
       <c r="C207">
-        <v>210.81</v>
+        <v>236.35</v>
       </c>
       <c r="D207">
         <v>172.13114929199219</v>
@@ -3614,7 +3617,7 @@
         <v>34</v>
       </c>
       <c r="C213">
-        <v>555.04999999999995</v>
+        <v>599.54</v>
       </c>
       <c r="D213">
         <v>446.62945556640619</v>
@@ -3628,7 +3631,7 @@
         <v>34</v>
       </c>
       <c r="C214">
-        <v>527.59</v>
+        <v>591.51</v>
       </c>
       <c r="D214">
         <v>423.97125244140619</v>
@@ -3712,7 +3715,7 @@
         <v>35</v>
       </c>
       <c r="C220">
-        <v>56.36</v>
+        <v>60.88</v>
       </c>
       <c r="D220">
         <v>46.071979522705078</v>
@@ -3726,7 +3729,7 @@
         <v>35</v>
       </c>
       <c r="C221">
-        <v>51.48</v>
+        <v>57.72</v>
       </c>
       <c r="D221">
         <v>43.699882507324219</v>
@@ -3810,7 +3813,7 @@
         <v>36</v>
       </c>
       <c r="C227">
-        <v>127.72</v>
+        <v>137.96</v>
       </c>
       <c r="D227">
         <v>109.9047317504883</v>
@@ -3824,7 +3827,7 @@
         <v>36</v>
       </c>
       <c r="C228">
-        <v>114.15</v>
+        <v>127.98</v>
       </c>
       <c r="D228">
         <v>100.6344680786133</v>
@@ -3908,7 +3911,7 @@
         <v>37</v>
       </c>
       <c r="C234">
-        <v>366.37</v>
+        <v>395.74</v>
       </c>
       <c r="D234">
         <v>300.50064086914062</v>
@@ -3922,7 +3925,7 @@
         <v>37</v>
       </c>
       <c r="C235">
-        <v>351.88</v>
+        <v>394.51</v>
       </c>
       <c r="D235">
         <v>297.9615478515625</v>
@@ -4006,7 +4009,7 @@
         <v>38</v>
       </c>
       <c r="C241">
-        <v>318.94</v>
+        <v>344.51</v>
       </c>
       <c r="D241">
         <v>262.28195190429688</v>
@@ -4020,7 +4023,7 @@
         <v>38</v>
       </c>
       <c r="C242">
-        <v>288.20999999999998</v>
+        <v>323.13</v>
       </c>
       <c r="D242">
         <v>250.71653747558591</v>
@@ -4104,7 +4107,7 @@
         <v>39</v>
       </c>
       <c r="C248">
-        <v>133.15</v>
+        <v>143.82</v>
       </c>
       <c r="D248">
         <v>112.29713439941411</v>
@@ -4118,7 +4121,7 @@
         <v>39</v>
       </c>
       <c r="C249">
-        <v>130.29</v>
+        <v>146.08000000000001</v>
       </c>
       <c r="D249">
         <v>111.9355850219727</v>
@@ -4202,7 +4205,7 @@
         <v>40</v>
       </c>
       <c r="C255">
-        <v>545.13</v>
+        <v>588.83000000000004</v>
       </c>
       <c r="D255">
         <v>364.44869995117188</v>
@@ -4216,7 +4219,7 @@
         <v>40</v>
       </c>
       <c r="C256">
-        <v>534.41999999999996</v>
+        <v>599.16999999999996</v>
       </c>
       <c r="D256">
         <v>370.34866333007812</v>
@@ -4300,7 +4303,7 @@
         <v>41</v>
       </c>
       <c r="C262">
-        <v>484.69</v>
+        <v>523.54</v>
       </c>
       <c r="D262">
         <v>374.64093017578119</v>
@@ -4314,7 +4317,7 @@
         <v>41</v>
       </c>
       <c r="C263">
-        <v>461.65</v>
+        <v>517.58000000000004</v>
       </c>
       <c r="D263">
         <v>351.193603515625</v>
@@ -4398,7 +4401,7 @@
         <v>42</v>
       </c>
       <c r="C269">
-        <v>229.42</v>
+        <v>247.81</v>
       </c>
       <c r="D269">
         <v>178.86540222167969</v>
@@ -4412,7 +4415,7 @@
         <v>42</v>
       </c>
       <c r="C270">
-        <v>220.4</v>
+        <v>247.1</v>
       </c>
       <c r="D270">
         <v>168.57325744628909</v>
@@ -4496,7 +4499,7 @@
         <v>43</v>
       </c>
       <c r="C276">
-        <v>659.86</v>
+        <v>712.75</v>
       </c>
       <c r="D276">
         <v>560.15576171875</v>
@@ -4510,7 +4513,7 @@
         <v>43</v>
       </c>
       <c r="C277">
-        <v>641.9</v>
+        <v>719.67</v>
       </c>
       <c r="D277">
         <v>544.0703125</v>
@@ -4594,7 +4597,7 @@
         <v>44</v>
       </c>
       <c r="C283">
-        <v>690.07</v>
+        <v>745.38</v>
       </c>
       <c r="D283">
         <v>589.21954345703125</v>
@@ -4608,7 +4611,7 @@
         <v>44</v>
       </c>
       <c r="C284">
-        <v>686.05</v>
+        <v>769.17</v>
       </c>
       <c r="D284">
         <v>587.2359619140625</v>
@@ -4692,7 +4695,7 @@
         <v>45</v>
       </c>
       <c r="C290">
-        <v>400.11</v>
+        <v>432.18</v>
       </c>
       <c r="D290">
         <v>313.35641479492188</v>
@@ -4706,7 +4709,7 @@
         <v>45</v>
       </c>
       <c r="C291">
-        <v>389.53</v>
+        <v>436.72</v>
       </c>
       <c r="D291">
         <v>303.9788818359375</v>
@@ -4790,7 +4793,7 @@
         <v>46</v>
       </c>
       <c r="C297">
-        <v>371.13</v>
+        <v>400.88</v>
       </c>
       <c r="D297">
         <v>314.9931640625</v>
@@ -4804,7 +4807,7 @@
         <v>46</v>
       </c>
       <c r="C298">
-        <v>352.96</v>
+        <v>395.72</v>
       </c>
       <c r="D298">
         <v>276.458251953125</v>
@@ -4888,7 +4891,7 @@
         <v>47</v>
       </c>
       <c r="C304">
-        <v>265.76</v>
+        <v>287.06</v>
       </c>
       <c r="D304">
         <v>222.97080993652341</v>
@@ -4902,7 +4905,7 @@
         <v>47</v>
       </c>
       <c r="C305">
-        <v>253.68</v>
+        <v>284.42</v>
       </c>
       <c r="D305">
         <v>209.507080078125</v>
@@ -4986,7 +4989,7 @@
         <v>48</v>
       </c>
       <c r="C311">
-        <v>397.85</v>
+        <v>429.74</v>
       </c>
       <c r="D311">
         <v>319.28244018554688</v>
@@ -5000,7 +5003,7 @@
         <v>48</v>
       </c>
       <c r="C312">
-        <v>379.8</v>
+        <v>425.82</v>
       </c>
       <c r="D312">
         <v>301.12625122070312</v>
@@ -5084,7 +5087,7 @@
         <v>49</v>
       </c>
       <c r="C318">
-        <v>226.82</v>
+        <v>245</v>
       </c>
       <c r="D318">
         <v>180.6082458496094</v>
@@ -5098,7 +5101,7 @@
         <v>49</v>
       </c>
       <c r="C319">
-        <v>218.23</v>
+        <v>244.67</v>
       </c>
       <c r="D319">
         <v>166.1491394042969</v>
@@ -5182,7 +5185,7 @@
         <v>50</v>
       </c>
       <c r="C325">
-        <v>424.34</v>
+        <v>458.35</v>
       </c>
       <c r="D325">
         <v>357.756591796875</v>
@@ -5196,7 +5199,7 @@
         <v>50</v>
       </c>
       <c r="C326">
-        <v>406.81</v>
+        <v>456.1</v>
       </c>
       <c r="D326">
         <v>340.0078125</v>
@@ -5280,7 +5283,7 @@
         <v>51</v>
       </c>
       <c r="C332">
-        <v>454.77</v>
+        <v>491.22</v>
       </c>
       <c r="D332">
         <v>368.85153198242188</v>
@@ -5294,7 +5297,7 @@
         <v>51</v>
       </c>
       <c r="C333">
-        <v>456.91</v>
+        <v>512.27</v>
       </c>
       <c r="D333">
         <v>356.481689453125</v>
@@ -5378,7 +5381,7 @@
         <v>52</v>
       </c>
       <c r="C339">
-        <v>442.94</v>
+        <v>478.45</v>
       </c>
       <c r="D339">
         <v>352.32785034179688</v>
@@ -5392,7 +5395,7 @@
         <v>52</v>
       </c>
       <c r="C340">
-        <v>435.53</v>
+        <v>488.3</v>
       </c>
       <c r="D340">
         <v>345.04641723632812</v>
@@ -5476,7 +5479,7 @@
         <v>53</v>
       </c>
       <c r="C346">
-        <v>298.75</v>
+        <v>322.7</v>
       </c>
       <c r="D346">
         <v>241.05657958984381</v>
@@ -5490,7 +5493,7 @@
         <v>53</v>
       </c>
       <c r="C347">
-        <v>295.55</v>
+        <v>331.36</v>
       </c>
       <c r="D347">
         <v>239.5348205566406</v>
@@ -5574,7 +5577,7 @@
         <v>54</v>
       </c>
       <c r="C353">
-        <v>412.57</v>
+        <v>445.64</v>
       </c>
       <c r="D353">
         <v>299.25491333007812</v>
@@ -5588,7 +5591,7 @@
         <v>54</v>
       </c>
       <c r="C354">
-        <v>393.99</v>
+        <v>441.72</v>
       </c>
       <c r="D354">
         <v>279.22247314453119</v>
@@ -5672,7 +5675,7 @@
         <v>55</v>
       </c>
       <c r="C360">
-        <v>304.44</v>
+        <v>328.84</v>
       </c>
       <c r="D360">
         <v>225.70362854003909</v>
@@ -5686,7 +5689,7 @@
         <v>55</v>
       </c>
       <c r="C361">
-        <v>287.24</v>
+        <v>322.04000000000002</v>
       </c>
       <c r="D361">
         <v>216.62199401855469</v>
@@ -5770,7 +5773,7 @@
         <v>56</v>
       </c>
       <c r="C367">
-        <v>425.4</v>
+        <v>459.5</v>
       </c>
       <c r="D367">
         <v>353.93728637695312</v>
@@ -5784,7 +5787,7 @@
         <v>56</v>
       </c>
       <c r="C368">
-        <v>405.79</v>
+        <v>454.95</v>
       </c>
       <c r="D368">
         <v>333.39663696289062</v>
@@ -5868,7 +5871,7 @@
         <v>57</v>
       </c>
       <c r="C374">
-        <v>743.36</v>
+        <v>802.95</v>
       </c>
       <c r="D374">
         <v>576.86328125</v>
@@ -5882,7 +5885,7 @@
         <v>57</v>
       </c>
       <c r="C375">
-        <v>716.55</v>
+        <v>803.37</v>
       </c>
       <c r="D375">
         <v>563.9332275390625</v>
@@ -5966,7 +5969,7 @@
         <v>58</v>
       </c>
       <c r="C381">
-        <v>328.53</v>
+        <v>354.86</v>
       </c>
       <c r="D381">
         <v>245.9314880371094</v>
@@ -5980,7 +5983,7 @@
         <v>58</v>
       </c>
       <c r="C382">
-        <v>305.52999999999997</v>
+        <v>342.55</v>
       </c>
       <c r="D382">
         <v>231.8921203613281</v>
@@ -6064,7 +6067,7 @@
         <v>59</v>
       </c>
       <c r="C388">
-        <v>503.73</v>
+        <v>544.11</v>
       </c>
       <c r="D388">
         <v>418.67843627929688</v>
@@ -6078,7 +6081,7 @@
         <v>59</v>
       </c>
       <c r="C389">
-        <v>490.96</v>
+        <v>550.44000000000005</v>
       </c>
       <c r="D389">
         <v>403.37539672851562</v>
@@ -6162,7 +6165,7 @@
         <v>60</v>
       </c>
       <c r="C395">
-        <v>213.8</v>
+        <v>230.94</v>
       </c>
       <c r="D395">
         <v>155.5415344238281</v>
@@ -6176,7 +6179,7 @@
         <v>60</v>
       </c>
       <c r="C396">
-        <v>207.97</v>
+        <v>233.17</v>
       </c>
       <c r="D396">
         <v>150.42573547363281</v>
@@ -6260,7 +6263,7 @@
         <v>61</v>
       </c>
       <c r="C402">
-        <v>444</v>
+        <v>479.59</v>
       </c>
       <c r="D402">
         <v>363.15606689453119</v>
@@ -6274,7 +6277,7 @@
         <v>61</v>
       </c>
       <c r="C403">
-        <v>428.97</v>
+        <v>480.94</v>
       </c>
       <c r="D403">
         <v>335.15362548828119</v>
@@ -6358,7 +6361,7 @@
         <v>62</v>
       </c>
       <c r="C409">
-        <v>158.26</v>
+        <v>170.95</v>
       </c>
       <c r="D409">
         <v>124.87844085693359</v>
@@ -6372,7 +6375,7 @@
         <v>62</v>
       </c>
       <c r="C410">
-        <v>146.72999999999999</v>
+        <v>164.51</v>
       </c>
       <c r="D410">
         <v>115.8423538208008</v>
@@ -6456,7 +6459,7 @@
         <v>63</v>
       </c>
       <c r="C416">
-        <v>164.41</v>
+        <v>177.59</v>
       </c>
       <c r="D416">
         <v>125.2539596557617</v>
@@ -6470,7 +6473,7 @@
         <v>63</v>
       </c>
       <c r="C417">
-        <v>153.41</v>
+        <v>172</v>
       </c>
       <c r="D417">
         <v>117.89703369140619</v>
@@ -6554,7 +6557,7 @@
         <v>64</v>
       </c>
       <c r="C423">
-        <v>373.49</v>
+        <v>403.43</v>
       </c>
       <c r="D423">
         <v>306.9039306640625</v>
@@ -6568,7 +6571,7 @@
         <v>64</v>
       </c>
       <c r="C424">
-        <v>359.31</v>
+        <v>402.84</v>
       </c>
       <c r="D424">
         <v>291.69692993164062</v>
@@ -6652,7 +6655,7 @@
         <v>65</v>
       </c>
       <c r="C430">
-        <v>177.37</v>
+        <v>191.59</v>
       </c>
       <c r="D430">
         <v>154.67900085449219</v>
@@ -6666,7 +6669,7 @@
         <v>65</v>
       </c>
       <c r="C431">
-        <v>169.19</v>
+        <v>189.69</v>
       </c>
       <c r="D431">
         <v>147.97740173339841</v>
@@ -6750,7 +6753,7 @@
         <v>66</v>
       </c>
       <c r="C437">
-        <v>210.55</v>
+        <v>227.43</v>
       </c>
       <c r="D437">
         <v>180.33653259277341</v>
@@ -6764,7 +6767,7 @@
         <v>66</v>
       </c>
       <c r="C438">
-        <v>195.46</v>
+        <v>219.14</v>
       </c>
       <c r="D438">
         <v>154.5112609863281</v>
@@ -6848,7 +6851,7 @@
         <v>67</v>
       </c>
       <c r="C444">
-        <v>334.27</v>
+        <v>361.06</v>
       </c>
       <c r="D444">
         <v>283.06735229492188</v>
@@ -6862,7 +6865,7 @@
         <v>67</v>
       </c>
       <c r="C445">
-        <v>321.72000000000003</v>
+        <v>360.7</v>
       </c>
       <c r="D445">
         <v>286.24636840820312</v>
@@ -6946,7 +6949,7 @@
         <v>68</v>
       </c>
       <c r="C451">
-        <v>299.10000000000002</v>
+        <v>323.08</v>
       </c>
       <c r="D451">
         <v>244.16505432128909</v>
@@ -6960,7 +6963,7 @@
         <v>68</v>
       </c>
       <c r="C452">
-        <v>301.33999999999997</v>
+        <v>337.85</v>
       </c>
       <c r="D452">
         <v>244.14167785644531</v>
@@ -7044,7 +7047,7 @@
         <v>69</v>
       </c>
       <c r="C458">
-        <v>414.19</v>
+        <v>447.39</v>
       </c>
       <c r="D458">
         <v>343.13284301757812</v>
@@ -7058,7 +7061,7 @@
         <v>69</v>
       </c>
       <c r="C459">
-        <v>401.63</v>
+        <v>450.29</v>
       </c>
       <c r="D459">
         <v>331.31100463867188</v>
@@ -7142,7 +7145,7 @@
         <v>70</v>
       </c>
       <c r="C465">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="D465">
         <v>0</v>
@@ -7156,7 +7159,7 @@
         <v>70</v>
       </c>
       <c r="C466">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="D466">
         <v>0</v>
@@ -7240,7 +7243,7 @@
         <v>71</v>
       </c>
       <c r="C472">
-        <v>329.99</v>
+        <v>356.44</v>
       </c>
       <c r="D472">
         <v>270.313720703125</v>
@@ -7254,7 +7257,7 @@
         <v>71</v>
       </c>
       <c r="C473">
-        <v>318.98</v>
+        <v>357.63</v>
       </c>
       <c r="D473">
         <v>268.12109375</v>
@@ -7338,7 +7341,7 @@
         <v>72</v>
       </c>
       <c r="C479">
-        <v>329.48</v>
+        <v>355.89</v>
       </c>
       <c r="D479">
         <v>256.146728515625</v>
@@ -7352,7 +7355,7 @@
         <v>72</v>
       </c>
       <c r="C480">
-        <v>318.8</v>
+        <v>357.42</v>
       </c>
       <c r="D480">
         <v>247.93061828613281</v>
@@ -7436,7 +7439,7 @@
         <v>73</v>
       </c>
       <c r="C486">
-        <v>37.520000000000003</v>
+        <v>40.53</v>
       </c>
       <c r="D486">
         <v>31.812496185302731</v>
@@ -7450,7 +7453,7 @@
         <v>73</v>
       </c>
       <c r="C487">
-        <v>38.450000000000003</v>
+        <v>43.11</v>
       </c>
       <c r="D487">
         <v>34.563056945800781</v>
@@ -7534,7 +7537,7 @@
         <v>74</v>
       </c>
       <c r="C493">
-        <v>206.51</v>
+        <v>223.06</v>
       </c>
       <c r="D493">
         <v>151.39799499511719</v>
@@ -7548,7 +7551,7 @@
         <v>74</v>
       </c>
       <c r="C494">
-        <v>205.16</v>
+        <v>230.02</v>
       </c>
       <c r="D494">
         <v>153.4849548339844</v>
@@ -7632,7 +7635,7 @@
         <v>75</v>
       </c>
       <c r="C500">
-        <v>492.58</v>
+        <v>532.05999999999995</v>
       </c>
       <c r="D500">
         <v>390.43856811523438</v>
@@ -7646,7 +7649,7 @@
         <v>75</v>
       </c>
       <c r="C501">
-        <v>473.93</v>
+        <v>531.35</v>
       </c>
       <c r="D501">
         <v>374.63519287109381</v>
@@ -7730,7 +7733,7 @@
         <v>76</v>
       </c>
       <c r="C507">
-        <v>110.65</v>
+        <v>119.52</v>
       </c>
       <c r="D507">
         <v>89.575096130371094</v>
@@ -7744,7 +7747,7 @@
         <v>76</v>
       </c>
       <c r="C508">
-        <v>110.1</v>
+        <v>123.44</v>
       </c>
       <c r="D508">
         <v>88.133705139160156</v>
@@ -7828,7 +7831,7 @@
         <v>77</v>
       </c>
       <c r="C514">
-        <v>121</v>
+        <v>130.69999999999999</v>
       </c>
       <c r="D514">
         <v>93.033905029296875</v>
@@ -7842,7 +7845,7 @@
         <v>77</v>
       </c>
       <c r="C515">
-        <v>121.27</v>
+        <v>135.96</v>
       </c>
       <c r="D515">
         <v>96.792472839355469</v>
@@ -7926,7 +7929,7 @@
         <v>78</v>
       </c>
       <c r="C521">
-        <v>64.59</v>
+        <v>69.77</v>
       </c>
       <c r="D521">
         <v>53.493202209472663</v>
@@ -7940,7 +7943,7 @@
         <v>78</v>
       </c>
       <c r="C522">
-        <v>65.56</v>
+        <v>73.5</v>
       </c>
       <c r="D522">
         <v>52.263774871826172</v>
@@ -8024,7 +8027,7 @@
         <v>79</v>
       </c>
       <c r="C528">
-        <v>170.16</v>
+        <v>183.8</v>
       </c>
       <c r="D528">
         <v>130.2481689453125</v>
@@ -8038,7 +8041,7 @@
         <v>79</v>
       </c>
       <c r="C529">
-        <v>173.8</v>
+        <v>194.86</v>
       </c>
       <c r="D529">
         <v>133.5830078125</v>
